--- a/byod/BYOD-Security-Remediation.xlsx
+++ b/byod/BYOD-Security-Remediation.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Remediation Plan" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Admin Consoles" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Remediation Plan'!$A$1:$L$19</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,11 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -120,9 +126,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -155,6 +161,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -566,94 +578,118 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Columns to fill in</t>
+          <t>Admin consoles</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Owner and Status are for you to complete. Status values: Not started, In progress, Done, Accepted risk. Everything else is reference content.</t>
+          <t>All steps are written as click paths in the Microsoft 365 admin consoles (no PowerShell). The 'Admin Consoles' sheet lists each console's URL and the least-privileged admin role needed. Tip: every console has a search box at the top if a menu has moved.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>One exception</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Priority 2 &gt; Owner: J. Smith &gt; Status: In progress</t>
+          <t>Read-only Outlook on the web for unmanaged devices (item 4, step 5) has no admin-center switch; use a Defender for Cloud Apps session policy, or one Exchange PowerShell command if you do not have that licence.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Criticality</t>
+          <t>Columns to fill in</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Critical = exploitable now and leads to data loss or account takeover; High = significant exposure; Medium = gaps in governance or defence in depth; Low = residual risk.</t>
+          <t>Owner and Status are for you to complete. Status values: Not started, In progress, Done, Accepted risk. Everything else is reference content.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Most controls need Microsoft Entra ID P1 and Intune, both in Microsoft 365 Business Premium (up to 300 users) and E3+EMS / E5. Risk-based policies need Entra ID P2.</t>
+          <t>Priority 2 &gt; Owner: J. Smith &gt; Status: In progress</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Recommended BYOD model</t>
+          <t>Criticality</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Phones/tablets: Intune app protection without enrolment (MAM). Personal Windows/macOS: browser-only or Edge with Windows MAM. Full desktop apps only on Intune-compliant devices.</t>
+          <t>Critical = exploitable now and leads to data loss or account takeover; High = significant exposure; Medium = gaps in governance or defence in depth; Low = residual risk.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Introduce Conditional Access policies in Report-only mode first and always exclude two monitored break-glass admin accounts.</t>
+          <t>Most controls need Microsoft Entra ID P1 and Intune, both in Microsoft 365 Business Premium (up to 300 users) and E3+EMS / E5. Risk-based policies need Entra ID P2.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Recommended BYOD model</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Microsoft renames portal menus and retires controls regularly (e.g. 'Require approved client app'). Confirm against current Microsoft Learn documentation before changing production.</t>
+          <t>Phones/tablets: Intune app protection without enrolment (MAM). Personal Windows/macOS: browser-only or Edge with Windows MAM. Full desktop apps only on Intune-compliant devices.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Caution</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Introduce Conditional Access policies in Report-only mode first and always exclude two monitored break-glass admin accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft renames portal menus and retires controls regularly (e.g. 'Require approved client app'). Menu paths are current as of October 2026; confirm against Microsoft Learn before changing production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Prepared</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
@@ -678,10 +714,10 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="95" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -720,7 +756,7 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Where to configure</t>
+          <t>Admin console</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
@@ -775,15 +811,15 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>1. Inventory current licences: Microsoft 365 admin center &gt; Billing &gt; Your products.
-2. Move users who access company data from personal devices to Microsoft 365 Business Premium (up to 300 users) or E3 + EMS / E5.
-3. Decide whether you need Entra ID P2 (risk-based Conditional Access) and Defender for Cloud Apps (browser session control); both are in E5 or available as add-ons.
-4. Assign licences to all users before building the policies below; unlicensed users are not covered by Intune app protection.</t>
+          <t>1. Microsoft 365 admin center &gt; Billing &gt; Licenses: note which products you own and how many are assigned.
+2. Microsoft 365 admin center &gt; Users &gt; Active users &gt; Filter &gt; Unlicensed users: identify anyone without a licence.
+3. Microsoft 365 admin center &gt; Billing &gt; Purchase services: buy Microsoft 365 Business Premium (up to 300 users) or E3 + EMS E3 / E5. Add Entra ID P2 or Defender for Cloud Apps only if you want items 5 (risk policies) and 9 (browser session control).
+4. Microsoft 365 admin center &gt; Users &gt; Active users &gt; select users &gt; Manage product licenses &gt; Replace: assign the new licence to everyone who will use a personal device. Unlicensed users are not covered by Intune app protection.</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 admin center &gt; Billing; Users &gt; Active users &gt; Licenses</t>
+          <t>Microsoft 365 admin center (admin.microsoft.com) &gt; Billing; Users &gt; Active users</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -793,7 +829,7 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Get-MgSubscribedSku | Select SkuPartNumber, ConsumedUnits; confirm every active user has Entra ID P1 + Intune service plans.</t>
+          <t>Microsoft 365 admin center &gt; Billing &gt; Licenses shows Business Premium (or E3+EMS/E5) assigned to every active user; the Unlicensed users filter returns nobody who uses company data.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -834,17 +870,18 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>1. If you have no Conditional Access licence, turn on Security Defaults (Entra admin center &gt; Identity &gt; Overview &gt; Properties).
-2. Otherwise create Conditional Access policies: 'Require MFA for all users' (all cloud apps) and 'Block legacy authentication' (Client apps = Exchange ActiveSync clients + Other clients).
-3. Start in Report-only mode for 1-2 weeks, review the sign-in logs, then switch to On.
-4. Exclude two cloud-only break-glass admin accounts, protected by FIDO2 keys and monitored.
-5. Move users to phishing-resistant methods (passkeys in Microsoft Authenticator, FIDO2 keys, Windows Hello) and use Authentication strengths to require them for admins.
-6. Disable POP/IMAP/SMTP AUTH where not needed: Set-CASMailbox -PopEnabled $false -ImapEnabled $false -SmtpClientAuthenticationDisabled $true (or via CAS mailbox plans).</t>
+          <t>1. No Conditional Access licence: Entra admin center &gt; Entra ID &gt; Overview &gt; Properties &gt; Manage security defaults &gt; Enabled. (Turn it off again once you build the policies below.)
+2. With Entra ID P1: Entra admin center &gt; Conditional Access &gt; Policies &gt; New policy from template &gt; 'Require multifactor authentication for all users' and 'Block legacy authentication'. Set each to Report-only.
+3. In each policy: Users &gt; Exclude &gt; add two cloud-only break-glass admin accounts.
+4. After 1-2 weeks, Entra admin center &gt; Sign-in logs &gt; filter Conditional Access = Report-only: failure to check who would be blocked, fix them, then set the policies to On.
+5. Entra admin center &gt; Authentication methods &gt; Policies: enable Passkey (FIDO2) and Microsoft Authenticator; then Conditional Access &gt; Authentication strengths &gt; use 'Phishing-resistant MFA' in a policy targeting admin roles.
+6. Exchange admin center &gt; Settings &gt; Mail flow &gt; tick 'Turn off SMTP AUTH protocol for your organization'.
+7. For users who do not need POP/IMAP: Microsoft 365 admin center &gt; Users &gt; Active users &gt; select user &gt; Mail &gt; Manage email apps &gt; untick POP, IMAP and Authenticated SMTP &gt; Save changes.</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Protection &gt; Conditional Access; Authentication methods; Exchange Online PowerShell</t>
+          <t>Entra admin center (entra.microsoft.com) &gt; Conditional Access, Authentication methods; Exchange admin center &gt; Settings; Microsoft 365 admin center &gt; Active users</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -854,7 +891,7 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Entra sign-in logs filtered on 'Client app = legacy' show only failures; Authentication methods &gt; User registration details shows 100% MFA-capable.</t>
+          <t>Entra admin center &gt; Sign-in logs &gt; filter Client app = the legacy client types: only failures appear. Entra admin center &gt; Authentication methods &gt; User registration details: every user is MFA capable.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -895,17 +932,17 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>1. Decide the BYOD model per platform. Recommended: iOS/Android = app protection without enrolment (MAM); Windows/macOS personal = browser-only or Edge with Windows MAM; full desktop apps only on Intune-compliant devices.
-2. Create a CA policy for iOS/Android: grant 'Require app protection policy' (the older 'Require approved client app' control is being retired).
-3. Create a CA policy for Windows/macOS desktop clients: 'Require device to be marked as compliant' (Client apps = Mobile apps and desktop clients).
-4. Create a CA policy for browsers on unmanaged devices: Session &gt; 'Use app enforced restrictions' (pairs with item 4 below).
-5. Block unsupported device platforms (e.g. Linux, unknown) unless there is a business need.
-6. Pilot with a test group in Report-only, then enforce.</t>
+          <t>Decide the model first: phones/tablets = app protection without enrolment; personal Windows/Mac = browser only (or Edge with Windows MAM); full desktop apps only on Intune-compliant devices.
+1. Entra admin center &gt; Conditional Access &gt; Policies &gt; New policy 'BYOD - mobile apps need app protection': Users = All users (exclude break-glass); Target resources = Office 365; Conditions &gt; Device platforms = iOS, Android; Grant = 'Require app protection policy'. (The older 'Require approved client app' control is being retired.)
+2. New policy 'Desktop apps need compliant device': Device platforms = Windows, macOS; Conditions &gt; Client apps = Mobile apps and desktop clients; Grant = 'Require device to be marked as compliant'.
+3. New policy 'Browser on unmanaged devices': Client apps = Browser; Session = 'Use app enforced restrictions' (works with the SharePoint/Outlook settings in item 4).
+4. New policy 'Block unknown platforms': Device platforms &gt; Include Any device &gt; Exclude Android, iOS, Windows, macOS; Grant = Block access.
+5. Create every policy as Report-only, test with Conditional Access &gt; Policies &gt; What If, then switch to On.</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Protection &gt; Conditional Access</t>
+          <t>Entra admin center (entra.microsoft.com) &gt; Conditional Access &gt; Policies</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -915,7 +952,7 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Use the Conditional Access 'What If' tool for a user on an unregistered iPhone and an unmanaged Windows PC; check sign-in logs show the expected grant control.</t>
+          <t>Entra admin center &gt; Conditional Access &gt; What If: a user on iOS gets 'Require app protection policy', on an unmanaged Windows desktop client gets 'Require compliant device'. Sign-in logs &gt; Conditional Access tab shows the expected policy applied.</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -956,28 +993,28 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>1. In Intune create App protection policies for iOS and Android targeting all users and core apps (Outlook, Teams, OneDrive, SharePoint, Word/Excel/PowerPoint, Edge). Start from the Microsoft 'Level 2 enhanced data protection' framework.
-2. Data settings: block backup to iCloud/Google, 'Send org data to other apps' = Policy managed apps, 'Save copies of org data' = Block (allow OneDrive/SharePoint only), restrict cut/copy/paste to policy-managed apps, encrypt org data, block screen capture (Android).
-3. Access settings: require app PIN or biometrics, re-check after 30 minutes of inactivity.
-4. SharePoint/OneDrive on unmanaged devices: Set-SPOTenant -ConditionalAccessPolicy AllowLimitedAccess (web view only, no download/print/sync).
-5. Outlook on the web on unmanaged devices: Set-OwaMailboxPolicy -Identity OwaMailboxPolicy-Default -ConditionalAccessPolicy ReadOnly (attachments viewable, not downloadable).
-6. Windows personal PCs: enable Intune 'Windows MAM' for Microsoft Edge so the browser is the protected container.
-7. Note: the OneDrive 'sync only on domain-joined PCs' setting needs on-premises AD and does not apply to a cloud-only tenant; use the compliant-device CA policy (item 3) to control sync.</t>
+          <t>1. Intune admin center &gt; Apps &gt; App protection policies &gt; Create policy &gt; iOS/iPadOS (repeat for Android). Apps: Target to 'All Microsoft apps' (or select Outlook, Teams, OneDrive, SharePoint, Word, Excel, PowerPoint, Edge). Assignments: All users.
+2. Data protection page: Backup org data to iTunes/iCloud/Google = Block; Send org data to other apps = Policy managed apps; Save copies of org data = Block, Allow user to save copies to = OneDrive for Business, SharePoint; Restrict cut, copy and paste = Policy managed apps with paste in; Encrypt org data = Require; Screen capture (Android) = Block.
+3. Access requirements page: PIN for access = Require (biometrics allowed); Recheck after (minutes of inactivity) = 30.
+4. SharePoint admin center &gt; Policies &gt; Access control &gt; Unmanaged devices &gt; 'Allow limited, web-only access' &gt; Save. (This also creates matching Conditional Access policies in Entra; review them there.)
+5. Outlook on the web: Exchange has no admin-center switch for read-only attachments. Use Defender portal &gt; Cloud apps &gt; Policies &gt; Policy management &gt; Create policy &gt; Session policy &gt; 'Block download based on real-time content inspection' scoped to unmanaged devices (needs Defender for Cloud Apps). Without that licence, the only option is one Exchange PowerShell command (Set-OwaMailboxPolicy ... -ConditionalAccessPolicy ReadOnly).
+6. Personal Windows PCs: Intune admin center &gt; Apps &gt; App protection policies &gt; Create policy &gt; Windows (Microsoft Edge), then in Entra a CA policy for Windows + Browser with Grant 'Require app protection policy'.
+7. The OneDrive 'sync only on domain-joined PCs' setting needs on-premises AD and does not apply to a cloud-only tenant; the compliant-device policy in item 3 controls sync instead.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Intune admin center &gt; Apps &gt; App protection policies; SharePoint Online PowerShell; Exchange Online PowerShell</t>
+          <t>Intune admin center (intune.microsoft.com) &gt; Apps &gt; App protection policies; SharePoint admin center &gt; Policies &gt; Access control; Defender portal &gt; Cloud apps</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Intune + Entra ID P1</t>
+          <t>Intune + Entra ID P1 (Defender for Cloud Apps for step 5)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>On a test personal phone, try to 'Save to Files' an Outlook attachment and paste mail text into a personal app (both blocked); open SharePoint in a browser on an unmanaged PC (download button absent).</t>
+          <t>On a test personal phone, 'Save to Files' from Outlook and pasting mail text into a personal app are both blocked. In a browser on an unmanaged PC, SharePoint shows the 'download disabled' banner. Intune admin center &gt; Apps &gt; Monitor &gt; App protection status lists the test user.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -1018,17 +1055,17 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>1. Require phishing-resistant MFA (passkeys / FIDO2) where possible; it defeats AiTM proxies.
-2. For unmanaged devices set Session controls: Sign-in frequency (e.g. 8-12 hours) and 'Persistent browser session' = Never persistent.
-3. Turn on Continuous Access Evaluation and, if you use named locations, strict location enforcement.
-4. Where supported, enable Token protection (CA session control) for Exchange/SharePoint/Teams on Windows; check current platform support before relying on it.
-5. With Entra ID P2, add risk-based policies: sign-in risk High/Medium = MFA, user risk High = secure password change.
-6. Prepare a response playbook: Revoke-MgUserSignInSession -UserId &lt;user&gt;, reset password, review inbox rules and forwarding (Get-InboxRule), and check audit logs.</t>
+          <t>1. Entra admin center &gt; Authentication methods &gt; Policies: enable Passkey (FIDO2) and roll out passkeys in Microsoft Authenticator; phishing-resistant methods defeat AiTM proxies.
+2. Entra admin center &gt; Conditional Access &gt; New policy 'Unmanaged device sessions': Conditions &gt; Filter for devices &gt; exclude compliant devices (device.isCompliant -eq True); Session &gt; Sign-in frequency = 8 hours and Persistent browser session = Never persistent.
+3. In the same policy, Session &gt; Customize continuous access evaluation: leave enabled; if you use named locations choose 'Strictly enforce location policies'.
+4. Where your platforms support it, Session &gt; 'Require token protection for sign-in sessions' for Exchange Online, SharePoint and Teams (check Microsoft's current platform list first).
+5. With Entra ID P2: new CA policies using Conditions &gt; Sign-in risk (High, Medium) = Require MFA, and Conditions &gt; User risk (High) = Require password change.
+6. Compromise playbook in the consoles: Microsoft 365 admin center &gt; Active users &gt; user &gt; Account &gt; 'Sign out of all sessions' (or Entra admin center &gt; Users &gt; user &gt; Revoke sessions); Reset password; Exchange admin center &gt; Mailboxes &gt; user &gt; Mail flow settings &gt; check Email forwarding; Purview portal &gt; Audit &gt; search activities 'New-InboxRule' / 'Set-InboxRule' for that user; Exchange admin center &gt; Reports &gt; Mail flow &gt; Auto forwarded messages.</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Conditional Access; Entra ID Protection; Microsoft Graph PowerShell</t>
+          <t>Entra admin center &gt; Conditional Access, Authentication methods, Users; Microsoft 365 admin center; Exchange admin center; Purview portal &gt; Audit</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -1038,7 +1075,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Sign-in logs show sign-in frequency enforced for unmanaged devices; run the playbook against a test account and confirm sessions end within minutes.</t>
+          <t>Entra admin center &gt; Sign-in logs &gt; a sign-in from an unmanaged device shows sign-in frequency applied. Run the playbook on a test account: the user is signed out of Outlook/Teams within minutes.</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -1080,15 +1117,16 @@
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>1. Rely on app protection (item 4) so corporate data lives only inside managed apps.
-2. Set conditional launch 'Offline grace period' to wipe data after e.g. 90 days without check-in.
-3. Add to the leaver and lost-device process: Intune &gt; Apps &gt; App selective wipe; disable the account; Revoke-MgUserSignInSession.
-4. For native mail apps that are still allowed: Clear-MobileDevice -Identity &lt;id&gt; -AccountOnly (Exchange account-only wipe, leaves personal data).
-5. Tell users how to report a lost device within hours, not days.</t>
+2. Intune admin center &gt; Apps &gt; App protection policies &gt; open each policy &gt; Properties &gt; Conditional launch &gt; Edit: Offline grace period = Wipe data after 90 days.
+3. Lost device or leaver: Intune admin center &gt; Apps &gt; App selective wipe &gt; Create wipe request &gt; choose the user and device.
+4. Microsoft 365 admin center &gt; Active users &gt; user &gt; Block sign-in, then Account &gt; 'Sign out of all sessions'.
+5. If native mail apps are still allowed: Exchange admin center &gt; Recipients &gt; Mailboxes &gt; select user &gt; Others &gt; Manage mobile devices &gt; select the device &gt; 'Account only remote wipe device' (removes the mailbox only, leaves personal data).
+6. Add these steps to the HR leaver checklist and tell users to report a lost device within hours.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Intune admin center &gt; Apps &gt; App selective wipe; Exchange Online PowerShell; HR offboarding procedure</t>
+          <t>Intune admin center &gt; Apps &gt; App selective wipe; Microsoft 365 admin center &gt; Active users; Exchange admin center &gt; Mailboxes</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1098,7 +1136,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Run a selective wipe against a test phone: corporate accounts and files disappear from Outlook/OneDrive/Teams, personal photos and apps remain.</t>
+          <t>Create a selective wipe for a test phone: Intune admin center &gt; Apps &gt; App selective wipe shows status Done; company accounts and files disappear from Outlook/OneDrive/Teams while personal photos and apps remain.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1139,15 +1177,15 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>1. In app protection policies set Conditional launch: minimum OS version (block or wipe below it), jailbroken/rooted = Block access, Play Integrity verdict = Basic integrity and certified device (Android), minimum app versions.
-2. Optionally connect Microsoft Defender for Endpoint on iOS/Android and set 'Max allowed device threat level' in conditional launch.
-3. For personal devices you do enrol (iOS/iPadOS User Enrollment, Android Work Profile), create compliance policies with minimum OS, passcode and encryption requirements.
-4. Set Intune compliance 'Mark devices with no compliance policy assigned as' = Not compliant.</t>
+          <t>1. Intune admin center &gt; Apps &gt; App protection policies &gt; open each policy &gt; Properties &gt; Conditional launch &gt; Edit. Device conditions: Jailbroken/rooted devices = Block access; Min OS version = current major minus one, action Block access; Play integrity verdict (Android) = Basic integrity &amp; device certification, Block access. App conditions: Min app version where needed.
+2. Optional mobile threat defence: Intune admin center &gt; Endpoint security &gt; Microsoft Defender for Endpoint &gt; turn on 'Connect Android/iOS devices to Microsoft Defender for Endpoint' for app protection policy evaluation; then in Conditional launch add Max allowed device threat level = Low.
+3. For personal devices you enrol (iOS User Enrollment, Android Work Profile): Intune admin center &gt; Devices &gt; Compliance &gt; Create policy: minimum OS, require passcode and encryption.
+4. Intune admin center &gt; Devices &gt; Compliance &gt; Compliance settings: 'Mark devices with no compliance policy assigned as' = Not compliant.</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Intune admin center &gt; Apps &gt; App protection policies &gt; Conditional launch; Devices &gt; Compliance</t>
+          <t>Intune admin center (intune.microsoft.com) &gt; Apps &gt; App protection policies; Devices &gt; Compliance; Endpoint security</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1157,7 +1195,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Intune &gt; Apps &gt; Monitor &gt; App protection status shows no users on blocked OS versions; test with an old OS emulator or device.</t>
+          <t>Intune admin center &gt; Apps &gt; Monitor &gt; App protection status &gt; App protection report: no users on blocked OS versions. A test device below the minimum OS is blocked on launch.</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -1198,15 +1236,16 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>1. Standardise on Outlook for iOS/Android and communicate the change in advance.
-2. Conditional Access: block 'Exchange ActiveSync clients' (or require app protection, which native apps cannot satisfy).
-3. Defence in depth: Set-ActiveSyncOrganizationSettings -DefaultAccessLevel Quarantine and approve only Outlook via device access rules, or disable ActiveSync for users who do not need it (Set-CASMailbox -ActiveSyncEnabled $false).
-4. Review which devices already sync: Get-MobileDevice -ResultSize Unlimited | Group DeviceOS, ClientType.</t>
+          <t>1. See who uses what: Microsoft 365 admin center &gt; Reports &gt; Usage &gt; Exchange &gt; Email apps usage.
+2. Announce the move to Outlook for iOS/Android, with a date.
+3. Entra admin center &gt; Conditional Access &gt; New policy 'Block ActiveSync': Conditions &gt; Client apps &gt; Exchange ActiveSync clients; Target resources = Office 365 Exchange Online; Grant = Block access. Report-only first, then On.
+4. Defence in depth: Exchange admin center &gt; Mobile &gt; Device access &gt; Edit: when a device that is not managed by a rule connects = Quarantine; then add a device access rule allowing Outlook.
+5. Users who need no mobile mail at all: Microsoft 365 admin center &gt; Active users &gt; user &gt; Mail &gt; Manage email apps &gt; untick Exchange ActiveSync.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Conditional Access; Exchange admin center &gt; Mobile; Exchange Online PowerShell</t>
+          <t>Entra admin center &gt; Conditional Access; Exchange admin center &gt; Mobile &gt; Device access; Microsoft 365 admin center &gt; Reports</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1216,7 +1255,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Adding the work account to iOS Mail fails; Get-MobileDevice shows only Outlook (ClientType REST/Outlook) after cleanup.</t>
+          <t>Adding the work account to iOS Mail fails. Microsoft 365 admin center &gt; Reports &gt; Usage &gt; Email apps usage shows Outlook for mobile only after cleanup.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -1257,16 +1296,16 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>1. Block desktop/mobile clients on non-compliant Windows/macOS (item 3, policy for desktop clients).
-2. Allow browser access with app-enforced restrictions (SharePoint limited access, OWA ReadOnly - see item 4).
-3. Preferably require Microsoft Edge with Windows MAM on personal Windows PCs (CA: Windows platform, browser, grant 'Require app protection policy').
-4. With Defender for Cloud Apps, use Conditional Access App Control session policies to block download / copy / print of sensitive content in any browser.
-5. Educate users that personal PCs are browser-only by design.</t>
+          <t>1. Desktop apps blocked on non-compliant Windows/macOS: the 'Desktop apps need compliant device' policy from item 3.
+2. Browser access limited: the SharePoint 'Allow limited, web-only access' setting and the browser policy from items 3-4.
+3. Preferred on personal Windows: Intune admin center &gt; Apps &gt; App protection policies &gt; Create policy &gt; Windows (Microsoft Edge) with Data protection &gt; Receive data from / Send data to = Org data sources only, Print org data = Block. Then Entra admin center &gt; Conditional Access &gt; New policy: Device platforms = Windows, Client apps = Browser, Grant = Require app protection policy. Users get the Edge work profile.
+4. With Defender for Cloud Apps: Defender portal &gt; Cloud apps &gt; Policies &gt; Policy management &gt; Create policy &gt; Session policy: Session control type = Control file download (with inspection), Activity source = device tag not Intune compliant, Action = Block (also add policies for print and copy/paste as needed).
+5. Explain to users that personal PCs are browser-only by design.</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Conditional Access; Intune &gt; App protection (Windows); Defender portal &gt; Cloud apps</t>
+          <t>Entra admin center &gt; Conditional Access; Intune admin center &gt; App protection policies (Windows); Defender portal (security.microsoft.com) &gt; Cloud apps</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1276,7 +1315,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>On a personal PC: Outlook desktop sign-in blocked, OWA attachments are view-only, SharePoint shows 'download disabled' banner.</t>
+          <t>On a personal PC: Outlook desktop sign-in is blocked, SharePoint shows the 'download disabled' banner, and (with Cloud Apps) a download attempt shows the block page. Defender portal &gt; Cloud apps &gt; Activity log records it.</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -1317,15 +1356,15 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>1. Entra admin center &gt; Devices &gt; Device settings: limit 'Maximum number of devices per user' (e.g. 5-10).
-2. Create a CA policy for the user action 'Register or join devices' requiring MFA (set 'Require MFA to register or join devices' to No when using the CA policy).
-3. Intune &gt; Devices &gt; Enrollment restrictions: block personally owned Windows/macOS enrolment if the BYOD model is MAM-only; allow iOS User Enrollment / Android Work Profile only.
-4. Schedule clean-up of devices inactive for 90+ days (Entra &gt; Devices &gt; All devices, filter Activity), disable first and delete after a grace period.</t>
+          <t>1. Entra admin center &gt; Devices &gt; Device settings: Maximum number of devices per user = 10 (or fewer).
+2. Entra admin center &gt; Conditional Access &gt; New policy: Target resources &gt; User actions &gt; 'Register or join devices'; Grant = Require multifactor authentication. Then in Devices &gt; Device settings set 'Require Multifactor Authentication to register or join devices' = No (the CA policy replaces it).
+3. Intune admin center &gt; Devices &gt; Enrollment &gt; Device platform restriction &gt; edit the default Windows and macOS restrictions: Personally owned devices = Block (if personal PCs are browser only). For iOS allow User Enrollment; for Android allow Work Profile only.
+4. Monthly: Entra admin center &gt; Devices &gt; All devices &gt; Columns: Activity &gt; filter devices inactive 90+ days &gt; Disable; delete after a further grace period.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Devices &gt; Device settings; Conditional Access; Intune &gt; Enrollment</t>
+          <t>Entra admin center &gt; Devices &gt; Device settings, All devices; Conditional Access; Intune admin center &gt; Devices &gt; Enrollment</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1335,7 +1374,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Registering a new device prompts for MFA; Intune enrollment of a personal Windows PC is blocked; stale-device report is reviewed monthly.</t>
+          <t>Registering a new device prompts for MFA. Enrolling a personal Windows PC into Intune is refused. Entra admin center &gt; Devices &gt; All devices shows no active devices older than 90 days.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1376,15 +1415,15 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>1. Entra admin center &gt; Enterprise apps &gt; Consent and permissions: allow user consent only for apps from verified publishers with low-impact permissions (or disable user consent).
-2. Enable the admin consent workflow so users can request apps and admins review them.
-3. Review existing grants: Enterprise apps &gt; filter 'Application type = all', check permissions and remove unknown apps.
-4. With Defender for Cloud Apps, enable app governance / OAuth app policies to alert on risky apps.</t>
+          <t>1. Entra admin center &gt; Enterprise apps &gt; Consent and permissions &gt; User consent settings: 'Allow user consent for apps from verified publishers, for selected permissions' (or 'Do not allow user consent').
+2. Same page &gt; Admin consent settings: Users can request admin consent = Yes; choose reviewers.
+3. Entra admin center &gt; Enterprise apps &gt; All applications &gt; Application type = All applications: open each unfamiliar app &gt; Permissions; remove apps you do not recognise (Properties &gt; Delete).
+4. With Defender for Cloud Apps: Defender portal &gt; Cloud apps &gt; App governance: turn on and review the predefined OAuth app policies.</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Enterprise applications &gt; Consent and permissions</t>
+          <t>Entra admin center &gt; Enterprise apps &gt; Consent and permissions; Defender portal &gt; Cloud apps &gt; App governance</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1394,7 +1433,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>A test user attempting to consent to an unverified app with Mail.Read sees 'Approval required'.</t>
+          <t>A test user who tries to consent to an unverified app requesting Mail.Read sees 'Approval required'. Entra admin center &gt; Enterprise apps &gt; Admin consent requests receives the request.</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -1435,16 +1474,16 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>1. Confirm the unified audit log is on: Get-AdminAuditLogConfig | fl UnifiedAuditLogIngestionEnabled.
-2. Export Entra sign-in and audit logs to a Log Analytics workspace or SIEM for 90+ days of retention.
-3. Use the Conditional Access insights and reporting workbook to see unmanaged-device sign-ins.
-4. Review Intune app protection reports monthly (Apps &gt; Monitor &gt; App protection status).
-5. Create alerts for new inbox forwarding rules, mass downloads and impossible travel (Defender portal alert policies).</t>
+          <t>1. Microsoft Purview portal &gt; Solutions &gt; Audit: if a banner says 'Start recording user and admin activity', select it (auditing is on by default in most tenants).
+2. Entra admin center &gt; Monitoring &amp; health &gt; Diagnostic settings &gt; Add diagnostic setting: send SignInLogs, NonInteractiveUserSignInLogs and AuditLogs to a Log Analytics workspace (Azure subscription) with 90+ days retention.
+3. Entra admin center &gt; Monitoring &amp; health &gt; Workbooks &gt; 'Conditional Access insights and reporting': review unmanaged-device sign-ins monthly.
+4. Intune admin center &gt; Apps &gt; Monitor &gt; App protection status: review monthly.
+5. Defender portal &gt; Email &amp; collaboration &gt; Policies &amp; rules &gt; Alert policy: make sure alerts for 'Suspicious email forwarding activity' and 'Creation of forwarding/redirect rule' are on and notify an admin mailbox.</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Monitoring &gt; Diagnostic settings; Purview portal &gt; Audit; Defender portal</t>
+          <t>Purview portal (purview.microsoft.com) &gt; Audit; Entra admin center &gt; Monitoring &amp; health; Defender portal &gt; Policies &amp; rules</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1454,7 +1493,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>A sign-in from a test unmanaged device can be found in the SIEM 60 days later.</t>
+          <t>Purview &gt; Audit search returns events from today. A sign-in from a test unmanaged device can still be found in Log Analytics 60 days later.</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1495,15 +1534,15 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>1. Create a small label taxonomy (Public, General, Confidential, Highly Confidential) in Microsoft Purview.
-2. Apply encryption to Confidential and above so files can only be opened by authorised users, and optionally block offline access for Highly Confidential.
-3. Configure DLP policies for Exchange, SharePoint, OneDrive and Teams to detect and block sharing of sensitive information types (payment cards, national IDs).
-4. Turn on default labelling for new documents and mail where appropriate.</t>
+          <t>1. Microsoft Purview portal &gt; Solutions &gt; Information protection &gt; Sensitivity labels &gt; Create a label: Public, General, Confidential, Highly Confidential.
+2. For Confidential and Highly Confidential: Items &gt; Control access (encryption) &gt; assign permissions to your organisation; for Highly Confidential set 'Allow offline access' = Never.
+3. Information protection &gt; Label publishing policies &gt; Publish labels to all users; optionally set a default label.
+4. Purview portal &gt; Solutions &gt; Data loss prevention &gt; Policies &gt; Create policy: use a template (e.g. Financial / Privacy for your country), locations Exchange, SharePoint, OneDrive, Teams, action Block sharing outside the organisation with policy tips. Start in simulation mode.</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Microsoft Purview portal &gt; Information protection; Data loss prevention</t>
+          <t>Microsoft Purview portal (purview.microsoft.com) &gt; Information protection; Data loss prevention</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -1513,7 +1552,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Open a Highly Confidential document as an unauthorised user (denied); DLP blocks emailing a test card number externally.</t>
+          <t>An unauthorised user cannot open a Highly Confidential test file. Emailing a test credit-card number externally triggers the DLP policy tip and appears under Purview &gt; Data loss prevention &gt; Alerts.</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -1554,16 +1593,16 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>1. Write a BYOD policy with HR and legal: eligible devices, required apps (Outlook, Teams, OneDrive), minimum OS, PIN/biometric, reporting loss within 24 hours, selective-wipe consent, what IT can and cannot see.
-2. Prefer MAM or user enrolment models so IT never sees personal apps, photos or location.
-3. Customise Intune Company Portal privacy messaging and terms and conditions.
-4. Require acknowledgement (Entra terms of use, enforceable via Conditional Access) before access.
-5. Review the policy annually.</t>
+          <t>1. Write the policy with HR and legal: eligible devices, required apps, minimum OS, PIN/biometric, report loss within 24 hours, consent to selective wipe, what IT can and cannot see.
+2. Entra admin center &gt; Conditional Access &gt; Terms of use &gt; New terms: upload the policy PDF, Require users to expand = On.
+3. Entra admin center &gt; Conditional Access &gt; New policy 'Accept BYOD terms': All users, Office 365, Grant = the terms of use you created.
+4. Intune admin center &gt; Tenant administration &gt; Customization &gt; edit: add privacy statement URL, support contact and the Company Portal message explaining what IT can see.
+5. Review the policy every year and publish a new terms-of-use version when it changes.</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>HR/legal; Entra admin center &gt; Identity governance &gt; Terms of use; Intune &gt; Tenant administration &gt; Customization</t>
+          <t>Entra admin center &gt; Conditional Access &gt; Terms of use; Intune admin center &gt; Tenant administration &gt; Customization</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1573,7 +1612,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Every BYOD user has accepted the current terms of use version (Terms of use report).</t>
+          <t>Entra admin center &gt; Conditional Access &gt; Terms of use &gt; select the terms &gt; View accepted/declined shows every BYOD user accepted the current version.</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -1614,15 +1653,15 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>1. Rely on app protection 'multi-identity' behaviour: org data cannot be saved to the personal account inside Outlook/OneDrive/Office (item 4 settings).
-2. Use Edge for Business profiles; on Windows MAM the work profile is the protected container.
-3. Configure Entra Tenant restrictions v2 to stop users signing in to other tenants on devices where it can be enforced (managed devices or via Global Secure Access).
-4. Restrict external sharing in SharePoint/OneDrive to existing guests or specific domains.</t>
+          <t>1. App protection (item 4) already separates accounts inside Outlook/OneDrive/Office: confirm 'Save copies of org data' = Block with only OneDrive for Business and SharePoint allowed.
+2. Personal Windows: the Edge work profile created by Windows MAM (item 9) keeps work browsing separate.
+3. Entra admin center &gt; External Identities &gt; Cross-tenant access settings &gt; Default settings &gt; Tenant restrictions: block access to other tenants for your users. Note it is only enforced on managed devices or through Global Secure Access, not on unmanaged personal devices.
+4. SharePoint admin center &gt; Policies &gt; Sharing: set external sharing to 'Existing guests' or 'New and existing guests' and limit by domain (More external sharing settings).</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Intune &gt; App protection; Entra admin center &gt; External identities &gt; Cross-tenant access; SharePoint admin center &gt; Sharing</t>
+          <t>Intune admin center &gt; App protection policies; Entra admin center &gt; External Identities; SharePoint admin center &gt; Policies &gt; Sharing</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1632,7 +1671,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>On a test phone, try to save a work attachment to the personal OneDrive account in the same app (blocked).</t>
+          <t>On a test phone, saving a work attachment to the personal OneDrive account in the same app is blocked.</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
@@ -1673,15 +1712,15 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>1. Run short onboarding training: installing Outlook/Teams, what app protection does, how to report loss or suspected compromise.
-2. Use Defender for Office 365 Attack simulation training (Plan 2) or another phishing simulator.
-3. Enable the Report Message / Report Phishing button in Outlook.
-4. Publish a one-page 'lost device' procedure with the helpdesk contact.</t>
+          <t>1. Run short onboarding training: installing Outlook/Teams from the official stores, what app protection does, how to report loss or compromise.
+2. Defender portal &gt; Email &amp; collaboration &gt; Attack simulation training &gt; Simulations &gt; Launch a simulation (Defender for Office 365 Plan 2).
+3. Defender portal &gt; Settings &gt; Email &amp; collaboration &gt; User reported settings: enable the Microsoft Report button in Outlook and set a reporting mailbox.
+4. Publish a one-page 'lost device' procedure with the helpdesk contact; link it in the Company Portal (Intune admin center &gt; Tenant administration &gt; Customization).</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Defender portal &gt; Email &amp; collaboration &gt; Attack simulation training; internal comms</t>
+          <t>Defender portal (security.microsoft.com) &gt; Attack simulation training; Settings &gt; Email &amp; collaboration</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -1691,7 +1730,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Training completion rate and simulated phish click rate tracked quarterly.</t>
+          <t>Defender portal &gt; Attack simulation training &gt; Reports: completion and click rates tracked quarterly. Reported messages appear under Actions &amp; submissions &gt; Submissions.</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1732,14 +1771,15 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>1. Define named locations for countries you operate in and block or require stronger MFA from others (do not rely on IP alone).
-2. Keep MFA and token controls (items 2 and 5) as the primary protection.
-3. Optionally evaluate Microsoft Entra Internet Access / Global Secure Access for compliant-network checks.</t>
+          <t>1. Entra admin center &gt; Conditional Access &gt; Named locations &gt; + Countries location: add the countries you operate in.
+2. Conditional Access &gt; New policy: Conditions &gt; Locations &gt; Include Any location, Exclude your countries location; Grant = Block access (or require phishing-resistant MFA). Exclude break-glass accounts and remember travelling staff.
+3. Keep MFA and session controls (items 2 and 5) as the main protection.
+4. Optional: Entra admin center &gt; Global Secure Access to add compliant-network checks.</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Entra admin center &gt; Conditional Access &gt; Named locations</t>
+          <t>Entra admin center &gt; Conditional Access &gt; Named locations, Policies</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -1749,7 +1789,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>A test sign-in through a VPN exit node in a blocked country is denied.</t>
+          <t>Conditional Access &gt; What If with a blocked country selected returns Block access; sign-in logs show the policy blocking a test sign-in through a foreign VPN.</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -1791,9 +1831,9 @@
       <c r="F19" s="7" t="inlineStr">
         <is>
           <t>1. Prefer blocking sync on unmanaged PCs (items 3 and 4) so this cannot occur.
-2. Know the recovery tools: OneDrive 'Restore your OneDrive' (30 days), recycle bins (93 days).
-3. Apply Purview retention policies to Exchange, SharePoint and OneDrive for business-critical data.
-4. Consider Microsoft 365 Backup or a third-party backup for longer recovery points.</t>
+2. Know the recovery paths: user's OneDrive &gt; Settings &gt; Restore your OneDrive (30 days); SharePoint site &gt; Recycle bin (93 days).
+3. Microsoft Purview portal &gt; Solutions &gt; Data lifecycle management &gt; Policies &gt; Retention policies &gt; New retention policy: Exchange mailboxes, SharePoint sites, OneDrive accounts; retain for the period your business needs.
+4. Microsoft 365 admin center &gt; Settings &gt; Microsoft 365 Backup: set up billing and backup policies for critical OneDrive accounts, SharePoint sites and mailboxes.</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1808,7 +1848,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Test-restore a deleted folder from a pilot user's OneDrive.</t>
+          <t>Restore a deleted test folder from a pilot user's OneDrive; Purview &gt; Data lifecycle management &gt; Retention policies shows the policy On for all three locations.</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -1969,4 +2009,200 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Used for</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Least-privileged role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft 365 admin center</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>https://admin.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Licences, users, email apps per user, sign out of sessions, usage reports, Microsoft 365 Backup</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Global Reader to view; User Administrator / Billing Administrator to change</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft Entra admin center</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>https://entra.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Conditional Access, authentication methods, device settings, enterprise app consent, terms of use, sign-in logs</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Conditional Access Administrator, Authentication Policy Administrator, Cloud Application Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft Intune admin center</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>https://intune.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>App protection policies, selective wipe, compliance, enrolment restrictions, Company Portal customisation</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Intune Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Exchange admin center</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>https://admin.exchange.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>SMTP AUTH, mobile device access, mailbox forwarding, account-only wipe, mail flow reports</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Exchange Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>SharePoint admin center</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>https://&lt;tenant&gt;-admin.sharepoint.com (or Microsoft 365 admin center &gt; Admin centers &gt; SharePoint)</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Unmanaged device access, external sharing</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>SharePoint Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft Defender portal</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>https://security.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Cloud Apps session policies and app governance, alert policies, attack simulation, user-reported settings</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Security Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft Purview portal</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>https://purview.microsoft.com</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Audit, sensitivity labels, DLP, retention</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Compliance Administrator</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>